--- a/data/trans_camb/P1804_2016_2023-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1804_2016_2023-Provincia-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-5,82</t>
+          <t>-6,03</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-10,62</t>
+          <t>-9,61</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-8,23</t>
+          <t>-7,8</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,83; -2,74</t>
+          <t>-9,6; -3,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,72; -6,16</t>
+          <t>-14,59; -5,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,26; -5,4</t>
+          <t>-10,59; -5,26</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-79,29%</t>
+          <t>-82,16%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-74,59%</t>
+          <t>-67,48%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-76,47%</t>
+          <t>-72,46%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-92,98; -37,56</t>
+          <t>-94,28; -51,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,44; -55,53</t>
+          <t>-80,2; -46,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,27; -60,34</t>
+          <t>-82,3; -56,87</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-4,15</t>
+          <t>-4,17</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-4,68</t>
+          <t>-4,54</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-4,44</t>
+          <t>-4,36</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,24; -2,04</t>
+          <t>-6,42; -2,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; -2,16</t>
+          <t>-7,19; -2,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,35; -3,0</t>
+          <t>-5,99; -2,82</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-91,59%</t>
+          <t>-92,05%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-72,15%</t>
+          <t>-70,02%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-80,28%</t>
+          <t>-78,97%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -8,88</t>
+          <t>-100,0; -53,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-87,38; -37,54</t>
+          <t>-87,44; -40,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-91,4; -59,75</t>
+          <t>-90,4; -57,96</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>3,58</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,57</t>
+          <t>2,58</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,04</t>
+          <t>-0,96; 3,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 7,15</t>
+          <t>0,17; 6,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,7</t>
+          <t>0,49; 4,68</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,69%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,66; 321,78</t>
+          <t>-36,96; 339,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 249,64</t>
+          <t>1,55; 257,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,52; 196,07</t>
+          <t>9,25; 198,8</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12,67</t>
+          <t>12,99</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-3,19</t>
+          <t>4,65</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,84</t>
+          <t>8,72</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,41; 20,69</t>
+          <t>5,42; 20,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 6,05</t>
+          <t>-1,97; 11,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 9,81</t>
+          <t>3,61; 13,64</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-10,86%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,07; 111,78</t>
+          <t>22,07; 112,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 22,37</t>
+          <t>-6,21; 44,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 41,03</t>
+          <t>13,12; 58,59</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-2,04</t>
+          <t>-2,1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-3,22</t>
+          <t>-3,29</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,62</t>
+          <t>-2,7</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,21</t>
+          <t>-5,11; -0,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,81; -0,49</t>
+          <t>-6,72; -0,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,22; -0,84</t>
+          <t>-5,3; -1,05</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-65,42%</t>
+          <t>-67,44%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-64,68%</t>
+          <t>-66,08%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-64,45%</t>
+          <t>-66,32%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-93,19; 59,73</t>
+          <t>-100,0; 53,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-85,63; -8,21</t>
+          <t>-87,92; -3,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-85,38; -24,31</t>
+          <t>-86,19; -31,91</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>6,29</t>
+          <t>6,09</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6,31</t>
+          <t>6,87</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6,24</t>
+          <t>6,43</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,4</t>
+          <t>4,09; 9,06</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,73; 9,52</t>
+          <t>3,17; 10,62</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,29; 8,56</t>
+          <t>4,34; 8,45</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>240,96%</t>
+          <t>262,56%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>468,16%</t>
+          <t>482,58%</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>41,66; 652,49</t>
+          <t>54,86; 758,2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>174,48; 1408,75</t>
+          <t>165,78; 1321,68</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>1,5</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 3,56</t>
+          <t>-1,9; 3,46</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 3,39</t>
+          <t>-0,6; 4,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,55</t>
+          <t>-0,57; 3,27</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-0,18%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-28,15; 93,3</t>
+          <t>-31,54; 91,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-51,51; 53,81</t>
+          <t>-6,85; 92,7</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-31,81; 49,44</t>
+          <t>-8,29; 63,65</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>-4,45</t>
+          <t>-4,06</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-7,29</t>
+          <t>-7,28</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-6,01</t>
+          <t>-5,72</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,8; -2,69</t>
+          <t>-6,02; -2,12</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,03; -5,12</t>
+          <t>-9,83; -4,99</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,62; -4,45</t>
+          <t>-7,46; -4,32</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>-76,81%</t>
+          <t>-70,03%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-73,74%</t>
+          <t>-73,68%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-76,08%</t>
+          <t>-72,43%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-91,08; -57,26</t>
+          <t>-86,16; -43,45</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-83,28; -58,25</t>
+          <t>-83,8; -59,54</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-85,93; -63,81</t>
+          <t>-81,25; -60,33</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>-2,36</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>-0,76</t>
         </is>
       </c>
     </row>
@@ -1339,17 +1339,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,59</t>
+          <t>-1,3; 1,28</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,95</t>
+          <t>-2,86; -0,14</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,7; -0,59</t>
+          <t>-1,77; 0,13</t>
         </is>
       </c>
     </row>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>-12,39%</t>
+          <t>-1,72%</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>-23,8%</t>
+          <t>-14,13%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-19,41%</t>
+          <t>-9,37%</t>
         </is>
       </c>
     </row>
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 10,24</t>
+          <t>-18,84; 21,92</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-38,52; -10,13</t>
+          <t>-26,97; -1,46</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-31,65; -7,88</t>
+          <t>-19,86; 1,92</t>
         </is>
       </c>
     </row>
